--- a/business_forms/050_digital_workforce_optimization_registration_form--business_forms.xlsx
+++ b/business_forms/050_digital_workforce_optimization_registration_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'software_engineer'}</t>
+          <t>software_engineer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Software Engineer'}</t>
+          <t>Software Engineer</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'data_scientist'}</t>
+          <t>data_scientist</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Data Scientist'}</t>
+          <t>Data Scientist</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'operations_manager'}</t>
+          <t>operations_manager</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Operations Manager'}</t>
+          <t>Operations Manager</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'direct'}</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Direct'}</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'indirect'}</t>
+          <t>indirect</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Indirect'}</t>
+          <t>Indirect</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Full time'}</t>
+          <t>Full time</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Part time'}</t>
+          <t>Part time</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'on_site'}</t>
+          <t>on_site</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'On site'}</t>
+          <t>On site</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'8_am_-_5_pm'}</t>
+          <t>8_am_-_5_pm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': '8 am - 5 pm'}</t>
+          <t>8 am - 5 pm</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'10_am_-_7_pm'}</t>
+          <t>10_am_-_7_pm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': '10 am - 7 pm'}</t>
+          <t>10 am - 7 pm</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'bi-annually'}</t>
+          <t>bi-annually</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Bi-annually'}</t>
+          <t>Bi-annually</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
